--- a/WebHost/wwwroot/eam/basexlsx/施工能耗月度报表模板.xlsx
+++ b/WebHost/wwwroot/eam/basexlsx/施工能耗月度报表模板.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>厦门港务疏浚工程有限公司</t>
   </si>
@@ -116,70 +116,40 @@
     <t>泵机总耗</t>
   </si>
   <si>
+    <t>{{Table&gt;&gt;List|MonthName}}</t>
+  </si>
+  <si>
+    <t>{{SHIPTIMES}}</t>
+  </si>
+  <si>
+    <t>{{ZYTIME}}</t>
+  </si>
+  <si>
+    <t>{{STOPTIME}}</t>
+  </si>
+  <si>
+    <t>{{DAILYCONSUMPTION}}</t>
+  </si>
+  <si>
+    <t>{{MASTER}}</t>
+  </si>
+  <si>
+    <t>{{AUXILIARY}}</t>
+  </si>
+  <si>
+    <t>{{PUMP}}</t>
+  </si>
+  <si>
+    <t>{{LUBRICATE|&gt;&gt;Table}}</t>
+  </si>
+  <si>
     <t>一月</t>
   </si>
   <si>
-    <t>{{Table&gt;&gt;List|SHIPTIMES}}</t>
-  </si>
-  <si>
-    <t>{{ZYTIME}}</t>
-  </si>
-  <si>
-    <t>{{STOPTIME}}</t>
-  </si>
-  <si>
-    <t>{{DAILYCONSUMPTION}}</t>
-  </si>
-  <si>
-    <t>{{MASTER}}</t>
-  </si>
-  <si>
-    <t>{{AUXILIARY}}</t>
-  </si>
-  <si>
-    <t>{{PUMP}}</t>
-  </si>
-  <si>
-    <t>{{LUBRICATE|&gt;&gt;Table}}</t>
-  </si>
-  <si>
-    <t>二月</t>
-  </si>
-  <si>
-    <t>三月</t>
-  </si>
-  <si>
-    <t>四月</t>
-  </si>
-  <si>
-    <t>五月</t>
-  </si>
-  <si>
-    <t>六月</t>
-  </si>
-  <si>
-    <t>七月</t>
-  </si>
-  <si>
-    <t>八月</t>
-  </si>
-  <si>
-    <t>九月</t>
-  </si>
-  <si>
-    <t>十月</t>
-  </si>
-  <si>
-    <t>十一月</t>
-  </si>
-  <si>
-    <t>十二月</t>
-  </si>
-  <si>
     <t>合计</t>
   </si>
   <si>
-    <t>{{ZYTIMETOTAL}}</t>
+    <t>{{SHIPTOTAL}}</t>
   </si>
   <si>
     <t>{{ZYTIMETOTAL}}小时</t>
@@ -1006,11 +976,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1353,7 +1323,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:J40"/>
+  <dimension ref="B3:J29"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.62962962962963" style="1" customWidth="1"/>
@@ -1479,394 +1449,251 @@
       <c r="B12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B13" s="14" t="s">
+    <row r="13" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B14" s="14" t="s">
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B14" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B15" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B18" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B19" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
+      <c r="B21" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" s="1" customFormat="1" hidden="1" customHeight="1" spans="2:10">
+      <c r="B22" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" s="1" customFormat="1" hidden="1" customHeight="1" spans="2:10">
+      <c r="B23" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" hidden="1" customHeight="1" spans="2:10">
+      <c r="B24" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" hidden="1" customHeight="1" spans="2:10">
+      <c r="B25" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:10">
+      <c r="B26" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B15" s="14" t="s">
+      <c r="C26" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B16" s="14" t="s">
+      <c r="D26" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B17" s="14" t="s">
+      <c r="E26" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B18" s="14" t="s">
+      <c r="F26" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B19" s="14" t="s">
+      <c r="G26" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B20" s="14" t="s">
+      <c r="H26" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B21" s="14" t="s">
+      <c r="I26" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B22" s="14" t="s">
+      <c r="J26" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="24.95" customHeight="1" spans="2:10">
-      <c r="B23" s="14" t="s">
+    </row>
+    <row r="27" customHeight="1" spans="2:10">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" customHeight="1" spans="7:9">
+      <c r="G28" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B24" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B27" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B28" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B30" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B31" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="24.95" hidden="1" customHeight="1" spans="2:10">
-      <c r="B32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-    </row>
-    <row r="33" s="1" customFormat="1" hidden="1" customHeight="1" spans="2:10">
-      <c r="B33" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-    </row>
-    <row r="34" s="1" customFormat="1" hidden="1" customHeight="1" spans="2:10">
-      <c r="B34" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-    </row>
-    <row r="35" hidden="1" customHeight="1" spans="2:10">
-      <c r="B35" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-    </row>
-    <row r="36" hidden="1" customHeight="1" spans="2:10">
-      <c r="B36" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-    </row>
-    <row r="37" customHeight="1" spans="2:10">
-      <c r="B37" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="2:10">
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="17"/>
-    </row>
-    <row r="39" customHeight="1" spans="7:9">
-      <c r="G39" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-    </row>
-    <row r="40" customHeight="1" spans="7:9">
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+    </row>
+    <row r="29" customHeight="1" spans="7:9">
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1877,21 +1704,21 @@
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B26:B27"/>
     <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="C26:C27"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D26:D27"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="E26:E27"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
     <mergeCell ref="J10:J11"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="G39:I40"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="G28:I29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="landscape"/>
